--- a/AAII_Financials/Yearly/UCAR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/UCAR_YR_FIN.xlsx
@@ -1861,7 +1861,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E42" s="3">
         <v>600</v>
@@ -1900,7 +1900,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>11900</v>
+        <v>13800</v>
       </c>
       <c r="E43" s="3">
         <v>7500</v>
@@ -1978,7 +1978,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>4200</v>
+        <v>2000</v>
       </c>
       <c r="E45" s="3">
         <v>1500</v>
@@ -2441,7 +2441,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2900</v>
+        <v>3200</v>
       </c>
       <c r="E58" s="3">
         <v>3400</v>
@@ -2480,7 +2480,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1700</v>
+        <v>1900</v>
       </c>
       <c r="E59" s="3">
         <v>1700</v>
